--- a/artfynd/A 59823-2022 artfynd.xlsx
+++ b/artfynd/A 59823-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59823-2022 artfynd.xlsx
+++ b/artfynd/A 59823-2022 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>126795784</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126795880</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>126795766</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126795923</v>
+        <v>126795931</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492296</v>
+        <v>492278</v>
       </c>
       <c r="R6" t="n">
-        <v>6946013</v>
+        <v>6946001</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126795931</v>
+        <v>126795923</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492278</v>
+        <v>492296</v>
       </c>
       <c r="R7" t="n">
-        <v>6946001</v>
+        <v>6946013</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126795643</v>
+        <v>126795891</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492273</v>
+        <v>492291</v>
       </c>
       <c r="R8" t="n">
-        <v>6946082</v>
+        <v>6945999</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,42 +1394,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126795843</v>
+        <v>126795643</v>
       </c>
       <c r="B9" t="n">
-        <v>98278</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1437,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492364</v>
+        <v>492273</v>
       </c>
       <c r="R9" t="n">
-        <v>6946007</v>
+        <v>6946082</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,37 +1495,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126795891</v>
+        <v>126795843</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>98353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492291</v>
+        <v>492364</v>
       </c>
       <c r="R10" t="n">
-        <v>6945999</v>
+        <v>6946007</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1604,7 @@
         <v>126795869</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>126795809</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59823-2022 artfynd.xlsx
+++ b/artfynd/A 59823-2022 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>126795784</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126795880</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>126795766</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>126795931</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126795923</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>126795891</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>126795643</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>126795843</v>
       </c>
       <c r="B10" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>126795869</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>126795809</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59823-2022 artfynd.xlsx
+++ b/artfynd/A 59823-2022 artfynd.xlsx
@@ -1498,7 +1498,7 @@
         <v>126795843</v>
       </c>
       <c r="B10" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59823-2022 artfynd.xlsx
+++ b/artfynd/A 59823-2022 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>126795784</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126795880</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>126795766</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>126795931</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126795923</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>126795891</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>126795643</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>126795843</v>
       </c>
       <c r="B10" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>126795869</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>126795809</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>126795632</v>
       </c>
       <c r="B13" t="n">
-        <v>56852</v>
+        <v>56856</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59823-2022 artfynd.xlsx
+++ b/artfynd/A 59823-2022 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>126795784</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126795880</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>126795766</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>126795931</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126795923</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>126795891</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>126795643</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>126795843</v>
       </c>
       <c r="B10" t="n">
-        <v>98364</v>
+        <v>98353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>126795869</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>126795809</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>126795632</v>
       </c>
       <c r="B13" t="n">
-        <v>56856</v>
+        <v>56852</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59823-2022 artfynd.xlsx
+++ b/artfynd/A 59823-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111439224</v>
+        <v>122195702</v>
       </c>
       <c r="B2" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Håkaberget (Håkaberget), Jmt</t>
+          <t>Mellansjöholmen, Mellansjöholmen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491944.26140267</v>
+        <v>492453</v>
       </c>
       <c r="R2" t="n">
-        <v>6946663.819588403</v>
+        <v>6946015</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Finns allmänt mycket Garnlav i området.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +774,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126795784</v>
+        <v>126795643</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -826,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492317</v>
+        <v>492273</v>
       </c>
       <c r="R3" t="n">
-        <v>6946040</v>
+        <v>6946082</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,14 +887,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126795880</v>
+        <v>126795766</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -927,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492305</v>
+        <v>492291</v>
       </c>
       <c r="R4" t="n">
-        <v>6946020</v>
+        <v>6946092</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,14 +988,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126795766</v>
+        <v>126795784</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1028,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492291</v>
+        <v>492317</v>
       </c>
       <c r="R5" t="n">
-        <v>6946092</v>
+        <v>6946040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,14 +1089,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126795931</v>
+        <v>126795809</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1129,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492278</v>
+        <v>492453</v>
       </c>
       <c r="R6" t="n">
-        <v>6946001</v>
+        <v>6945972</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,14 +1190,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126795923</v>
+        <v>126795869</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1230,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492296</v>
+        <v>492339</v>
       </c>
       <c r="R7" t="n">
-        <v>6946013</v>
+        <v>6946018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,14 +1291,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126795891</v>
+        <v>126795880</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1331,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492291</v>
+        <v>492305</v>
       </c>
       <c r="R8" t="n">
-        <v>6945999</v>
+        <v>6946020</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,14 +1392,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126795643</v>
+        <v>126795891</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1432,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492273</v>
+        <v>492291</v>
       </c>
       <c r="R9" t="n">
-        <v>6946082</v>
+        <v>6945999</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,42 +1493,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126795843</v>
+        <v>126795923</v>
       </c>
       <c r="B10" t="n">
-        <v>98364</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1538,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492364</v>
+        <v>492296</v>
       </c>
       <c r="R10" t="n">
-        <v>6946007</v>
+        <v>6946013</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,14 +1594,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126795869</v>
+        <v>126795931</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1639,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492339</v>
+        <v>492278</v>
       </c>
       <c r="R11" t="n">
-        <v>6946018</v>
+        <v>6946001</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,14 +1695,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126795809</v>
+        <v>127422499</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1731,19 +1724,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Markustjärnen, Jmt</t>
+          <t>Markustjärnen, Markustjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492453</v>
+        <v>492161</v>
       </c>
       <c r="R12" t="n">
-        <v>6945972</v>
+        <v>6945949</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,12 +1760,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1784,7 +1784,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1803,60 +1802,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126795632</v>
+        <v>127422504</v>
       </c>
       <c r="B13" t="n">
-        <v>56856</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102613</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Markustjärnen, Jmt</t>
+          <t>Mellansjöholmen, Mellansjöholmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492239</v>
+        <v>492159</v>
       </c>
       <c r="R13" t="n">
-        <v>6946086</v>
+        <v>6945932</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1880,12 +1867,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1900,15 +1897,453 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126795540</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Markustjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>492145</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6945943</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126795632</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Markustjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>492239</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6946086</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126795843</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Markustjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>492364</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6946007</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126795613</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Markustjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>492247</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6945967</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59823-2022 artfynd.xlsx
+++ b/artfynd/A 59823-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122195702</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795643</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795766</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795784</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795809</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795869</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795880</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795891</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1591,6 +1636,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795923</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795931</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422499</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127422504</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2023,6 +2088,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795540</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2132,6 +2202,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795632</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2238,6 +2313,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795843</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,8 +2424,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795613</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>